--- a/4k1s/TPO4-1/lab4/4.2. Техники тест-дизайна.xlsx
+++ b/4k1s/TPO4-1/lab4/4.2. Техники тест-дизайна.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\General\BELSTU\4k1s\TPO4-1\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFD41A1-7DDE-4694-9BBA-2396663341B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EE365C-CCA6-4C7B-954B-25AA154394E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Задание 1" sheetId="1" r:id="rId1"/>
@@ -758,10 +758,10 @@
     <t>Сокращение методом попарного тестирования: 16 тестов вместо 32</t>
   </si>
   <si>
-    <t>Проверка покрытия: всего пар значений из разных групп — 32 (транспорт×период 16, транспорт×оплата 8, период×оплата 8). В 16 тестах покрыты все 32.</t>
-  </si>
-  <si>
     <t>Почему именно 16, а не меньше: при попарном покрытии должна встретиться каждая пара значений из разных групп. Только у двух групп по 4 варианта это уже 4 × 4 = 16 пар, и в одном тесте встречается ровно одна такая пара — значит меньше 16 тестов не хватит. Двухвариантная группа «Способ оплаты» раскладывается по этим 16 строкам без добавления новых тестов: способ оплаты чередуется так, чтобы каждый вид транспорта и каждый период встретились и с оплатой картой, и с оплатой наличными.</t>
+  </si>
+  <si>
+    <t>Проверка покрытия: всего пар значений из разных групп — 32 (транспорт × период 16, транспорт × оплата 8, период × оплата 8). В 16 тестах покрыты все 32.</t>
   </si>
 </sst>
 </file>
@@ -853,7 +853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -885,10 +885,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1193,7 +1199,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D69"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1201,7 +1207,7 @@
     <col min="4" max="4" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1209,7 +1215,7 @@
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1223,7 +1229,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -1231,7 +1237,7 @@
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
     </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1245,7 +1251,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1259,7 +1265,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -1273,7 +1279,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -1287,7 +1293,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -1301,7 +1307,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -1315,7 +1321,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>28</v>
       </c>
@@ -1323,7 +1329,7 @@
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
     </row>
-    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -1337,7 +1343,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
@@ -1351,7 +1357,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>33</v>
       </c>
@@ -1365,7 +1371,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>35</v>
       </c>
@@ -1379,7 +1385,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>37</v>
       </c>
@@ -1393,7 +1399,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>39</v>
       </c>
@@ -1407,7 +1413,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>42</v>
       </c>
@@ -1421,7 +1427,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>46</v>
       </c>
@@ -1435,7 +1441,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>49</v>
       </c>
@@ -1449,7 +1455,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>52</v>
       </c>
@@ -1457,7 +1463,7 @@
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>53</v>
       </c>
@@ -1471,7 +1477,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>54</v>
       </c>
@@ -1485,7 +1491,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>57</v>
       </c>
@@ -1499,7 +1505,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>60</v>
       </c>
@@ -1513,7 +1519,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>63</v>
       </c>
@@ -1527,7 +1533,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>67</v>
       </c>
@@ -1541,7 +1547,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>70</v>
       </c>
@@ -1555,7 +1561,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>73</v>
       </c>
@@ -1569,7 +1575,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>76</v>
       </c>
@@ -1583,7 +1589,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>80</v>
       </c>
@@ -1597,7 +1603,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>83</v>
       </c>
@@ -1611,7 +1617,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>86</v>
       </c>
@@ -1625,7 +1631,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>89</v>
       </c>
@@ -1639,7 +1645,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>92</v>
       </c>
@@ -1653,7 +1659,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>95</v>
       </c>
@@ -1661,7 +1667,7 @@
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>96</v>
       </c>
@@ -1675,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>97</v>
       </c>
@@ -1689,7 +1695,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>101</v>
       </c>
@@ -1703,7 +1709,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>104</v>
       </c>
@@ -1717,7 +1723,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>107</v>
       </c>
@@ -1731,7 +1737,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>110</v>
       </c>
@@ -1745,7 +1751,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>113</v>
       </c>
@@ -1759,7 +1765,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>116</v>
       </c>
@@ -1773,7 +1779,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>119</v>
       </c>
@@ -1787,7 +1793,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>122</v>
       </c>
@@ -1801,7 +1807,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>125</v>
       </c>
@@ -1815,7 +1821,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>128</v>
       </c>
@@ -1829,7 +1835,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>131</v>
       </c>
@@ -1843,7 +1849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>134</v>
       </c>
@@ -1857,7 +1863,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>137</v>
       </c>
@@ -1871,7 +1877,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>140</v>
       </c>
@@ -1885,7 +1891,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>143</v>
       </c>
@@ -1899,7 +1905,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>146</v>
       </c>
@@ -1913,7 +1919,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>149</v>
       </c>
@@ -1927,7 +1933,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>153</v>
       </c>
@@ -1941,7 +1947,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>156</v>
       </c>
@@ -1955,7 +1961,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>159</v>
       </c>
@@ -1969,7 +1975,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>163</v>
       </c>
@@ -1983,7 +1989,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
         <v>166</v>
       </c>
@@ -1991,7 +1997,7 @@
       <c r="C60" s="12"/>
       <c r="D60" s="12"/>
     </row>
-    <row r="61" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>167</v>
       </c>
@@ -2005,7 +2011,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>171</v>
       </c>
@@ -2019,7 +2025,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>175</v>
       </c>
@@ -2033,7 +2039,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>179</v>
       </c>
@@ -2047,7 +2053,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>181</v>
       </c>
@@ -2061,7 +2067,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>184</v>
       </c>
@@ -2075,7 +2081,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>188</v>
       </c>
@@ -2089,7 +2095,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>191</v>
       </c>
@@ -2103,7 +2109,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>194</v>
       </c>
@@ -2133,7 +2139,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
@@ -2142,7 +2148,7 @@
     <col min="7" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>197</v>
       </c>
@@ -2155,8 +2161,8 @@
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
         <v>198</v>
       </c>
       <c r="B3" s="10"/>
@@ -2168,7 +2174,7 @@
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>199</v>
       </c>
@@ -2197,8 +2203,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
         <v>200</v>
       </c>
       <c r="B5" s="12"/>
@@ -2210,7 +2216,7 @@
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>201</v>
       </c>
@@ -2239,7 +2245,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>204</v>
       </c>
@@ -2268,7 +2274,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>205</v>
       </c>
@@ -2297,8 +2303,8 @@
         <v>203</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
         <v>206</v>
       </c>
       <c r="B9" s="12"/>
@@ -2310,7 +2316,7 @@
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>207</v>
       </c>
@@ -2339,8 +2345,8 @@
         <v>211</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
         <v>212</v>
       </c>
       <c r="B13" s="10"/>
@@ -2352,7 +2358,7 @@
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
     </row>
-    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>199</v>
       </c>
@@ -2372,7 +2378,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>216</v>
       </c>
@@ -2392,7 +2398,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>219</v>
       </c>
@@ -2412,7 +2418,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>221</v>
       </c>
@@ -2432,7 +2438,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>223</v>
       </c>
@@ -2452,8 +2458,8 @@
         <v>224</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
         <v>225</v>
       </c>
       <c r="B20" s="10"/>
@@ -2462,7 +2468,7 @@
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -2470,7 +2476,7 @@
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -2493,16 +2499,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I65"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>226</v>
       </c>
@@ -2510,15 +2516,15 @@
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
         <v>227</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>228</v>
       </c>
@@ -2532,7 +2538,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -2546,7 +2552,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -2560,7 +2566,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -2574,7 +2580,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -2588,7 +2594,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>5</v>
       </c>
@@ -2602,7 +2608,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>6</v>
       </c>
@@ -2616,7 +2622,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>7</v>
       </c>
@@ -2630,7 +2636,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>8</v>
       </c>
@@ -2644,7 +2650,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>9</v>
       </c>
@@ -2658,7 +2664,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>10</v>
       </c>
@@ -2672,7 +2678,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>11</v>
       </c>
@@ -2686,7 +2692,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>12</v>
       </c>
@@ -2700,7 +2706,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>13</v>
       </c>
@@ -2714,7 +2720,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>14</v>
       </c>
@@ -2728,7 +2734,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>15</v>
       </c>
@@ -2742,7 +2748,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>16</v>
       </c>
@@ -2756,7 +2762,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>17</v>
       </c>
@@ -2770,7 +2776,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>18</v>
       </c>
@@ -2784,7 +2790,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>19</v>
       </c>
@@ -2798,7 +2804,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>20</v>
       </c>
@@ -2812,7 +2818,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>21</v>
       </c>
@@ -2826,7 +2832,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>22</v>
       </c>
@@ -2840,7 +2846,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>23</v>
       </c>
@@ -2854,7 +2860,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>24</v>
       </c>
@@ -2868,7 +2874,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>25</v>
       </c>
@@ -2882,7 +2888,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>26</v>
       </c>
@@ -2896,7 +2902,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>27</v>
       </c>
@@ -2910,7 +2916,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>28</v>
       </c>
@@ -2924,7 +2930,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>29</v>
       </c>
@@ -2938,7 +2944,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>30</v>
       </c>
@@ -2952,7 +2958,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>31</v>
       </c>
@@ -2966,7 +2972,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>32</v>
       </c>
@@ -2980,15 +2986,15 @@
         <v>235</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="15" t="s">
         <v>242</v>
       </c>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>228</v>
       </c>
@@ -3002,7 +3008,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>1</v>
       </c>
@@ -3015,8 +3021,9 @@
       <c r="D41" s="7" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I41" s="16"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>2</v>
       </c>
@@ -3030,7 +3037,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <v>3</v>
       </c>
@@ -3044,7 +3051,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>4</v>
       </c>
@@ -3058,7 +3065,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
         <v>5</v>
       </c>
@@ -3072,7 +3079,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
         <v>6</v>
       </c>
@@ -3086,7 +3093,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
         <v>7</v>
       </c>
@@ -3100,7 +3107,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>8</v>
       </c>
@@ -3114,7 +3121,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <v>9</v>
       </c>
@@ -3128,7 +3135,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>10</v>
       </c>
@@ -3142,7 +3149,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
         <v>11</v>
       </c>
@@ -3156,7 +3163,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <v>12</v>
       </c>
@@ -3170,7 +3177,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
         <v>13</v>
       </c>
@@ -3184,7 +3191,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
         <v>14</v>
       </c>
@@ -3198,7 +3205,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
         <v>15</v>
       </c>
@@ -3212,7 +3219,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <v>16</v>
       </c>
@@ -3226,47 +3233,47 @@
         <v>234</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="15" t="s">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="B58" s="17"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
+    </row>
+    <row r="59" spans="1:4" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="17"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="13" t="s">
         <v>243</v>
-      </c>
-      <c r="B58" s="10"/>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="10"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="15" t="s">
-        <v>244</v>
       </c>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="10"/>
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="10"/>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="10"/>
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
       <c r="D64" s="10"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="10"/>
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
